--- a/Data/AOBA/Fortified Features Framework - 3498575851/1.6/3498575851.xlsx
+++ b/Data/AOBA/Fortified Features Framework - 3498575851/1.6/3498575851.xlsx
@@ -8,8 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Main_260306" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="251028" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Main_260329" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="260306" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="251028" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,8 +21,30 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>알 수 없는 작성자</author>
+  </authors>
+  <commentList>
+    <comment ref="E192" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="나눔고딕"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2026-03-22에 새로 추가된 노드들 (5개)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="774">
   <si>
     <t xml:space="preserve">Class+Node [(Identifier (Key)]</t>
   </si>
@@ -2284,6 +2307,66 @@
   </si>
   <si>
     <t xml:space="preserve">{0}% 방어도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+FFF_NextRaidIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFF_NextRaidIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated raid time: {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 습격까지 예상 시간: {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+FFF_NextStrikeIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFF_NextStrikeIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated strike time: {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 공습까지 예상 시간: {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+FFF_NextStrikeStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFF_NextStrikeStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air support status: {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항공 지원 상태: {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+FFF_Status_Standby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFF_Status_Standby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standby (Waiting for target)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대기 중 (표적 지정 대기)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+FFF_Site_LocalMonitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFF_Site_LocalMonitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local monitoring (Offline)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현지 감시 중 (오프라인)</t>
   </si>
 </sst>
 </file>
@@ -2293,7 +2376,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2315,6 +2398,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2359,12 +2447,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2557,6 +2653,4172 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F1048576"/>
+  <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="60.52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="F50" s="0" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="F61" s="0" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="F65" s="0" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>254</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="F66" s="0" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F67" s="0" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="F68" s="0" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="F69" s="0" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="F70" s="0" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="F71" s="0" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="F72" s="0" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="F73" s="0" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="F80" s="0" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="F84" s="0" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="F85" s="0" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="F86" s="0" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
+        <v>338</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="F87" s="0" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="F88" s="0" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="F89" s="0" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="F90" s="0" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="F91" s="0" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>358</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>360</v>
+      </c>
+      <c r="F92" s="0" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
+        <v>362</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>363</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="F93" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="F94" s="0" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="E95" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="F95" s="0" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="F96" s="0" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="F97" s="0" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="F98" s="0" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="F99" s="0" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="E100" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="F100" s="0" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="F101" s="0" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="F102" s="0" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>403</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="F103" s="0" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="F104" s="0" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>407</v>
+      </c>
+      <c r="E105" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="F105" s="0" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="F106" s="0" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="E107" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="F107" s="0" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="E108" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="F108" s="0" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C109" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="E109" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="F109" s="0" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C110" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="F110" s="0" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="F111" s="0" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C112" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="F112" s="0" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C113" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="F113" s="0" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C114" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="F114" s="0" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C115" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="F115" s="0" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="F116" s="0" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C117" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="E117" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="F117" s="0" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C118" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="E118" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="F118" s="0" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C119" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="F119" s="0" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C120" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="E120" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="F121" s="0" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C122" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="E122" s="0" t="s">
+        <v>476</v>
+      </c>
+      <c r="F122" s="0" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C123" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="E123" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="F123" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C124" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="F124" s="0" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C125" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="E125" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="F125" s="0" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C126" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="F126" s="0" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C127" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="E127" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="F127" s="0" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="B128" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C128" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="F128" s="0" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="s">
+        <v>502</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C129" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="E129" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="F129" s="0" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C130" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="E130" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="F130" s="0" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="E131" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="F131" s="0" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C132" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="E132" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="F132" s="0" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C133" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="E133" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="F133" s="0" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C134" s="0" t="s">
+        <v>523</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="F134" s="0" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="s">
+        <v>526</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C135" s="0" t="s">
+        <v>527</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="F135" s="0" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C136" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="E136" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="F136" s="0" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B137" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C137" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="E137" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="F137" s="0" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="0" t="s">
+        <v>538</v>
+      </c>
+      <c r="B138" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>539</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="F138" s="0" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="B139" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>543</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>544</v>
+      </c>
+      <c r="F139" s="0" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="0" t="s">
+        <v>546</v>
+      </c>
+      <c r="B140" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C140" s="0" t="s">
+        <v>547</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>548</v>
+      </c>
+      <c r="F140" s="0" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="0" t="s">
+        <v>550</v>
+      </c>
+      <c r="B141" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C141" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="F141" s="0" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="0" t="s">
+        <v>554</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C142" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>556</v>
+      </c>
+      <c r="F142" s="0" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="s">
+        <v>558</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C143" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="F143" s="0" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="E144" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="F144" s="0" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C145" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="E145" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="F145" s="0" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="s">
+        <v>570</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C146" s="0" t="s">
+        <v>571</v>
+      </c>
+      <c r="E146" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="F146" s="0" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C147" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>576</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C149" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="F149" s="0" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C150" s="0" t="s">
+        <v>587</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="F150" s="0" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C151" s="0" t="s">
+        <v>591</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>592</v>
+      </c>
+      <c r="F151" s="0" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C152" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>596</v>
+      </c>
+      <c r="F152" s="0" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C153" s="0" t="s">
+        <v>599</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="F153" s="0" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C154" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="F154" s="0" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="F155" s="0" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="B156" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C156" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="E156" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="F156" s="0" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="B157" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C157" s="0" t="s">
+        <v>615</v>
+      </c>
+      <c r="E157" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="F157" s="0" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="B158" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C158" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="E158" s="0" t="s">
+        <v>620</v>
+      </c>
+      <c r="F158" s="0" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="0" t="s">
+        <v>622</v>
+      </c>
+      <c r="B159" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C159" s="0" t="s">
+        <v>623</v>
+      </c>
+      <c r="E159" s="0" t="s">
+        <v>624</v>
+      </c>
+      <c r="F159" s="0" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="B160" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C160" s="0" t="s">
+        <v>627</v>
+      </c>
+      <c r="E160" s="0" t="s">
+        <v>628</v>
+      </c>
+      <c r="F160" s="0" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0" t="s">
+        <v>630</v>
+      </c>
+      <c r="B161" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C161" s="0" t="s">
+        <v>631</v>
+      </c>
+      <c r="E161" s="0" t="s">
+        <v>632</v>
+      </c>
+      <c r="F161" s="0" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="B162" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C162" s="0" t="s">
+        <v>635</v>
+      </c>
+      <c r="E162" s="0" t="s">
+        <v>636</v>
+      </c>
+      <c r="F162" s="0" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="0" t="s">
+        <v>638</v>
+      </c>
+      <c r="B163" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C163" s="0" t="s">
+        <v>639</v>
+      </c>
+      <c r="E163" s="0" t="s">
+        <v>640</v>
+      </c>
+      <c r="F163" s="0" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="0" t="s">
+        <v>642</v>
+      </c>
+      <c r="B164" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C164" s="0" t="s">
+        <v>643</v>
+      </c>
+      <c r="E164" s="0" t="s">
+        <v>644</v>
+      </c>
+      <c r="F164" s="0" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="0" t="s">
+        <v>646</v>
+      </c>
+      <c r="B165" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C165" s="0" t="s">
+        <v>647</v>
+      </c>
+      <c r="E165" s="0" t="s">
+        <v>648</v>
+      </c>
+      <c r="F165" s="0" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="0" t="s">
+        <v>650</v>
+      </c>
+      <c r="B166" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C166" s="0" t="s">
+        <v>651</v>
+      </c>
+      <c r="E166" s="0" t="s">
+        <v>652</v>
+      </c>
+      <c r="F166" s="0" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="0" t="s">
+        <v>654</v>
+      </c>
+      <c r="B167" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C167" s="0" t="s">
+        <v>655</v>
+      </c>
+      <c r="E167" s="0" t="s">
+        <v>656</v>
+      </c>
+      <c r="F167" s="0" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="B168" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C168" s="0" t="s">
+        <v>659</v>
+      </c>
+      <c r="E168" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="F168" s="0" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="0" t="s">
+        <v>662</v>
+      </c>
+      <c r="B169" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C169" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="E169" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="F169" s="0" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="B170" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C170" s="0" t="s">
+        <v>667</v>
+      </c>
+      <c r="E170" s="0" t="s">
+        <v>668</v>
+      </c>
+      <c r="F170" s="0" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="0" t="s">
+        <v>670</v>
+      </c>
+      <c r="B171" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C171" s="0" t="s">
+        <v>671</v>
+      </c>
+      <c r="E171" s="0" t="s">
+        <v>672</v>
+      </c>
+      <c r="F171" s="0" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="0" t="s">
+        <v>674</v>
+      </c>
+      <c r="B172" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C172" s="0" t="s">
+        <v>675</v>
+      </c>
+      <c r="E172" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="F172" s="0" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0" t="s">
+        <v>678</v>
+      </c>
+      <c r="B173" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C173" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="E173" s="0" t="s">
+        <v>680</v>
+      </c>
+      <c r="F173" s="0" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="0" t="s">
+        <v>682</v>
+      </c>
+      <c r="B174" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C174" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="E174" s="0" t="s">
+        <v>684</v>
+      </c>
+      <c r="F174" s="0" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="0" t="s">
+        <v>686</v>
+      </c>
+      <c r="B175" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C175" s="0" t="s">
+        <v>687</v>
+      </c>
+      <c r="E175" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="F175" s="0" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A176" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="B176" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C176" s="0" t="s">
+        <v>691</v>
+      </c>
+      <c r="E176" s="0" t="s">
+        <v>692</v>
+      </c>
+      <c r="F176" s="0" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="0" t="s">
+        <v>694</v>
+      </c>
+      <c r="B177" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C177" s="0" t="s">
+        <v>695</v>
+      </c>
+      <c r="E177" s="0" t="s">
+        <v>696</v>
+      </c>
+      <c r="F177" s="0" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A178" s="0" t="s">
+        <v>698</v>
+      </c>
+      <c r="B178" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C178" s="0" t="s">
+        <v>699</v>
+      </c>
+      <c r="E178" s="0" t="s">
+        <v>700</v>
+      </c>
+      <c r="F178" s="0" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="0" t="s">
+        <v>702</v>
+      </c>
+      <c r="B179" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C179" s="0" t="s">
+        <v>703</v>
+      </c>
+      <c r="E179" s="0" t="s">
+        <v>704</v>
+      </c>
+      <c r="F179" s="0" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A180" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="B180" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C180" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="E180" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="F180" s="0" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="0" t="s">
+        <v>710</v>
+      </c>
+      <c r="B181" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C181" s="0" t="s">
+        <v>711</v>
+      </c>
+      <c r="E181" s="0" t="s">
+        <v>712</v>
+      </c>
+      <c r="F181" s="0" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A182" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="B182" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C182" s="0" t="s">
+        <v>715</v>
+      </c>
+      <c r="E182" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="F182" s="0" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="0" t="s">
+        <v>718</v>
+      </c>
+      <c r="B183" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C183" s="0" t="s">
+        <v>719</v>
+      </c>
+      <c r="E183" s="0" t="s">
+        <v>720</v>
+      </c>
+      <c r="F183" s="0" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A184" s="0" t="s">
+        <v>722</v>
+      </c>
+      <c r="B184" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C184" s="0" t="s">
+        <v>723</v>
+      </c>
+      <c r="E184" s="0" t="s">
+        <v>724</v>
+      </c>
+      <c r="F184" s="0" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A185" s="0" t="s">
+        <v>726</v>
+      </c>
+      <c r="B185" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C185" s="0" t="s">
+        <v>727</v>
+      </c>
+      <c r="E185" s="0" t="s">
+        <v>728</v>
+      </c>
+      <c r="F185" s="0" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="B186" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C186" s="0" t="s">
+        <v>731</v>
+      </c>
+      <c r="E186" s="0" t="s">
+        <v>732</v>
+      </c>
+      <c r="F186" s="0" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="0" t="s">
+        <v>734</v>
+      </c>
+      <c r="B187" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C187" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="E187" s="0" t="s">
+        <v>736</v>
+      </c>
+      <c r="F187" s="0" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="0" t="s">
+        <v>738</v>
+      </c>
+      <c r="B188" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C188" s="0" t="s">
+        <v>739</v>
+      </c>
+      <c r="E188" s="0" t="s">
+        <v>740</v>
+      </c>
+      <c r="F188" s="0" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="0" t="s">
+        <v>742</v>
+      </c>
+      <c r="B189" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C189" s="0" t="s">
+        <v>743</v>
+      </c>
+      <c r="E189" s="0" t="s">
+        <v>744</v>
+      </c>
+      <c r="F189" s="0" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A190" s="0" t="s">
+        <v>746</v>
+      </c>
+      <c r="B190" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C190" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="E190" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="F190" s="0" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="0" t="s">
+        <v>750</v>
+      </c>
+      <c r="B191" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C191" s="0" t="s">
+        <v>751</v>
+      </c>
+      <c r="E191" s="0" t="s">
+        <v>752</v>
+      </c>
+      <c r="F191" s="0" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="0" t="s">
+        <v>754</v>
+      </c>
+      <c r="B192" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C192" s="0" t="s">
+        <v>755</v>
+      </c>
+      <c r="E192" s="0" t="s">
+        <v>756</v>
+      </c>
+      <c r="F192" s="0" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="B193" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C193" s="0" t="s">
+        <v>759</v>
+      </c>
+      <c r="E193" s="0" t="s">
+        <v>760</v>
+      </c>
+      <c r="F193" s="0" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="0" t="s">
+        <v>762</v>
+      </c>
+      <c r="B194" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C194" s="0" t="s">
+        <v>763</v>
+      </c>
+      <c r="E194" s="0" t="s">
+        <v>764</v>
+      </c>
+      <c r="F194" s="0" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="0" t="s">
+        <v>766</v>
+      </c>
+      <c r="B195" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C195" s="0" t="s">
+        <v>767</v>
+      </c>
+      <c r="E195" s="0" t="s">
+        <v>768</v>
+      </c>
+      <c r="F195" s="0" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="B196" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="C196" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="E196" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="F196" s="0" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,보통"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,보통"&amp;12&amp;Kffffff페이지 &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2568,7 +6830,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="7" style="0" width="7.63"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -2588,7 +6850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>6</v>
       </c>
@@ -2605,7 +6867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>11</v>
       </c>
@@ -2622,7 +6884,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>15</v>
       </c>
@@ -2639,7 +6901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>19</v>
       </c>
@@ -2656,7 +6918,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>23</v>
       </c>
@@ -2673,7 +6935,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>28</v>
       </c>
@@ -2690,7 +6952,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>32</v>
       </c>
@@ -2707,7 +6969,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>37</v>
       </c>
@@ -2724,7 +6986,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>41</v>
       </c>
@@ -2741,7 +7003,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>45</v>
       </c>
@@ -2758,7 +7020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>49</v>
       </c>
@@ -2775,7 +7037,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>53</v>
       </c>
@@ -2792,7 +7054,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>57</v>
       </c>
@@ -2809,7 +7071,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>62</v>
       </c>
@@ -2826,7 +7088,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>66</v>
       </c>
@@ -2843,7 +7105,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
         <v>69</v>
       </c>
@@ -2860,7 +7122,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
         <v>74</v>
       </c>
@@ -2877,7 +7139,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>78</v>
       </c>
@@ -2894,7 +7156,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>82</v>
       </c>
@@ -6638,7 +10900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6646,2327 +10908,2327 @@
   <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultColWidth="12.046875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="7" style="0" width="7.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="58.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="52.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="22.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="46.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="46.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="7" style="2" width="7.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="2" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C21" s="0" t="s">
+      <c r="B21" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C22" s="0" t="s">
+      <c r="B22" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C23" s="0" t="s">
+      <c r="B23" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="2" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C24" s="0" t="s">
+      <c r="B24" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="2" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C25" s="0" t="s">
+      <c r="B25" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="2" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C26" s="0" t="s">
+      <c r="B26" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="2" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B27" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C27" s="0" t="s">
+      <c r="B27" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="2" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B28" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C28" s="0" t="s">
+      <c r="B28" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="2" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B29" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C29" s="0" t="s">
+      <c r="B29" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="2" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C30" s="0" t="s">
+      <c r="B30" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="2" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B31" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C31" s="0" t="s">
+      <c r="B31" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C32" s="0" t="s">
+      <c r="B32" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="2" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B33" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C33" s="0" t="s">
+      <c r="B33" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="2" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B34" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C34" s="0" t="s">
+      <c r="B34" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="2" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B35" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C35" s="0" t="s">
+      <c r="B35" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="2" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C36" s="0" t="s">
+      <c r="B36" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="2" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B37" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C37" s="0" t="s">
+      <c r="B37" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C38" s="0" t="s">
+      <c r="B38" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="2" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="0" t="s">
+      <c r="B39" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="2" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B40" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C40" s="0" t="s">
+      <c r="B40" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="2" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B41" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C41" s="0" t="s">
+      <c r="B41" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="2" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B42" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C42" s="0" t="s">
+      <c r="B42" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="2" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B43" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C43" s="0" t="s">
+      <c r="B43" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="E43" s="0" t="s">
+      <c r="E43" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="2" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C44" s="0" t="s">
+      <c r="B44" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="2" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B45" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C45" s="0" t="s">
+      <c r="B45" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E45" s="0" t="s">
+      <c r="E45" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="2" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B46" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C46" s="0" t="s">
+      <c r="B46" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="E46" s="0" t="s">
+      <c r="E46" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="2" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B47" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C47" s="0" t="s">
+      <c r="B47" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="E47" s="0" t="s">
+      <c r="E47" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="2" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B48" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C48" s="0" t="s">
+      <c r="B48" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="E48" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="2" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C49" s="0" t="s">
+      <c r="B49" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="E49" s="0" t="s">
+      <c r="E49" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="2" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B50" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C50" s="0" t="s">
+      <c r="B50" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E50" s="0" t="s">
+      <c r="E50" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="2" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B51" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C51" s="0" t="s">
+      <c r="B51" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="E51" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="2" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B52" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="0" t="s">
+      <c r="B52" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="2" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B53" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C53" s="0" t="s">
+      <c r="B53" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="E53" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="2" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B54" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C54" s="0" t="s">
+      <c r="B54" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="E54" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="2" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B55" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C55" s="0" t="s">
+      <c r="B55" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="E55" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="2" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B56" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C56" s="0" t="s">
+      <c r="B56" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E56" s="0" t="s">
+      <c r="E56" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="2" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B57" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C57" s="0" t="s">
+      <c r="B57" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="E57" s="0" t="s">
+      <c r="E57" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="2" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B58" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C58" s="0" t="s">
+      <c r="B58" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="E58" s="0" t="s">
+      <c r="E58" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="2" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B59" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C59" s="0" t="s">
+      <c r="B59" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="E59" s="0" t="s">
+      <c r="E59" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="2" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B60" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C60" s="0" t="s">
+      <c r="B60" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="E60" s="0" t="s">
+      <c r="E60" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="2" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B61" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C61" s="0" t="s">
+      <c r="B61" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="E61" s="0" t="s">
+      <c r="E61" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="2" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B62" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C62" s="0" t="s">
+      <c r="B62" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="E62" s="0" t="s">
+      <c r="E62" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="2" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B63" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C63" s="0" t="s">
+      <c r="B63" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="E63" s="0" t="s">
+      <c r="E63" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="2" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B64" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C64" s="0" t="s">
+      <c r="B64" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E64" s="0" t="s">
+      <c r="E64" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="2" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B65" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C65" s="0" t="s">
+      <c r="B65" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E65" s="0" t="s">
+      <c r="E65" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="2" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B66" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C66" s="0" t="s">
+      <c r="B66" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E66" s="0" t="s">
+      <c r="E66" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="2" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B67" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C67" s="0" t="s">
+      <c r="B67" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E67" s="0" t="s">
+      <c r="E67" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="2" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B68" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C68" s="0" t="s">
+      <c r="B68" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E68" s="0" t="s">
+      <c r="E68" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="2" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B69" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C69" s="0" t="s">
+      <c r="B69" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E69" s="0" t="s">
+      <c r="E69" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B70" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C70" s="0" t="s">
+      <c r="B70" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="E70" s="0" t="s">
+      <c r="E70" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="2" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="B71" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C71" s="0" t="s">
+      <c r="B71" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="E71" s="0" t="s">
+      <c r="E71" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="2" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="B72" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C72" s="0" t="s">
+      <c r="B72" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="E72" s="0" t="s">
+      <c r="E72" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="2" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B73" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C73" s="0" t="s">
+      <c r="B73" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="E73" s="0" t="s">
+      <c r="E73" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="2" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B74" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C74" s="0" t="s">
+      <c r="B74" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="E74" s="0" t="s">
+      <c r="E74" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="2" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B75" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C75" s="0" t="s">
+      <c r="B75" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="E75" s="0" t="s">
+      <c r="E75" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="2" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B76" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C76" s="0" t="s">
+      <c r="B76" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="E76" s="0" t="s">
+      <c r="E76" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="2" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B77" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C77" s="0" t="s">
+      <c r="B77" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="E77" s="0" t="s">
+      <c r="E77" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="2" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="B78" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C78" s="0" t="s">
+      <c r="B78" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="E78" s="0" t="s">
+      <c r="E78" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="3" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B79" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C79" s="0" t="s">
+      <c r="B79" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="E79" s="0" t="s">
+      <c r="E79" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="2" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B80" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C80" s="0" t="s">
+      <c r="B80" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="E80" s="0" t="s">
+      <c r="E80" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="2" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B81" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C81" s="0" t="s">
+      <c r="B81" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="E81" s="0" t="s">
+      <c r="E81" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="2" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B82" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C82" s="0" t="s">
+      <c r="B82" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="E82" s="0" t="s">
+      <c r="E82" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="2" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="B83" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C83" s="0" t="s">
+      <c r="B83" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="E83" s="0" t="s">
+      <c r="E83" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="2" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B84" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C84" s="0" t="s">
+      <c r="B84" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="E84" s="0" t="s">
+      <c r="E84" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="2" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="B85" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C85" s="0" t="s">
+      <c r="B85" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="E85" s="0" t="s">
+      <c r="E85" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="2" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="B86" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C86" s="0" t="s">
+      <c r="B86" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="E86" s="0" t="s">
+      <c r="E86" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="2" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B87" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C87" s="0" t="s">
+      <c r="B87" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="E87" s="0" t="s">
+      <c r="E87" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="2" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B88" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C88" s="0" t="s">
+      <c r="B88" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="E88" s="0" t="s">
+      <c r="E88" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="2" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B89" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C89" s="0" t="s">
+      <c r="B89" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="E89" s="0" t="s">
+      <c r="E89" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="2" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B90" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C90" s="0" t="s">
+      <c r="B90" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="E90" s="0" t="s">
+      <c r="E90" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="2" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B91" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C91" s="0" t="s">
+      <c r="B91" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="E91" s="0" t="s">
+      <c r="E91" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="2" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B92" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C92" s="0" t="s">
+      <c r="B92" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="E92" s="0" t="s">
+      <c r="E92" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" s="2" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B93" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C93" s="0" t="s">
+      <c r="B93" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="E93" s="0" t="s">
+      <c r="E93" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" s="2" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B94" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C94" s="0" t="s">
+      <c r="B94" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="E94" s="0" t="s">
+      <c r="E94" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" s="2" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B95" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C95" s="0" t="s">
+      <c r="B95" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E95" s="0" t="s">
+      <c r="E95" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" s="2" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B96" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C96" s="0" t="s">
+      <c r="B96" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="E96" s="0" t="s">
+      <c r="E96" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" s="2" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B97" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C97" s="0" t="s">
+      <c r="B97" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="E97" s="0" t="s">
+      <c r="E97" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" s="2" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B98" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C98" s="0" t="s">
+      <c r="B98" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="E98" s="0" t="s">
+      <c r="E98" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="F98" s="2" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="B99" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C99" s="0" t="s">
+      <c r="B99" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="E99" s="0" t="s">
+      <c r="E99" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="F99" s="0" t="s">
+      <c r="F99" s="2" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B100" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C100" s="0" t="s">
+      <c r="B100" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="E100" s="0" t="s">
+      <c r="E100" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="F100" s="2" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B101" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C101" s="0" t="s">
+      <c r="B101" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="E101" s="0" t="s">
+      <c r="E101" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="F101" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B102" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C102" s="0" t="s">
+      <c r="B102" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="E102" s="0" t="s">
+      <c r="E102" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="F102" s="2" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B103" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C103" s="0" t="s">
+      <c r="B103" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="E103" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="F103" s="2" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="B104" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C104" s="0" t="s">
+      <c r="B104" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E104" s="0" t="s">
+      <c r="E104" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="F104" s="2" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B105" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C105" s="0" t="s">
+      <c r="B105" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="E105" s="0" t="s">
+      <c r="E105" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" s="2" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="B106" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C106" s="0" t="s">
+      <c r="B106" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="E106" s="0" t="s">
+      <c r="E106" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" s="2" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B107" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C107" s="0" t="s">
+      <c r="B107" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="E107" s="0" t="s">
+      <c r="E107" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="F107" s="2" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B108" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C108" s="0" t="s">
+      <c r="B108" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="E108" s="0" t="s">
+      <c r="E108" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="F108" s="2" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B109" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C109" s="0" t="s">
+      <c r="B109" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="E109" s="0" t="s">
+      <c r="E109" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" s="2" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="B110" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C110" s="0" t="s">
+      <c r="B110" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="E110" s="0" t="s">
+      <c r="E110" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="F110" s="2" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B111" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C111" s="0" t="s">
+      <c r="B111" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="E111" s="0" t="s">
+      <c r="E111" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="F111" s="2" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="A112" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B112" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C112" s="0" t="s">
+      <c r="B112" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="E112" s="0" t="s">
+      <c r="E112" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="F112" s="2" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+      <c r="A113" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B113" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C113" s="0" t="s">
+      <c r="B113" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="E113" s="0" t="s">
+      <c r="E113" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="F113" s="0" t="s">
+      <c r="F113" s="2" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="A114" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B114" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C114" s="0" t="s">
+      <c r="B114" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="E114" s="0" t="s">
+      <c r="E114" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="F114" s="2" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="A115" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B115" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C115" s="0" t="s">
+      <c r="B115" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="E115" s="0" t="s">
+      <c r="E115" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="F115" s="0" t="s">
+      <c r="F115" s="2" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B116" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C116" s="0" t="s">
+      <c r="B116" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="E116" s="0" t="s">
+      <c r="E116" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="F116" s="0" t="s">
+      <c r="F116" s="2" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="A117" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="B117" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C117" s="0" t="s">
+      <c r="B117" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="E117" s="0" t="s">
+      <c r="E117" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="F117" s="0" t="s">
+      <c r="F117" s="2" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="A118" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="B118" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C118" s="0" t="s">
+      <c r="B118" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="E118" s="0" t="s">
+      <c r="E118" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="F118" s="0" t="s">
+      <c r="F118" s="2" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="A119" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="B119" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C119" s="0" t="s">
+      <c r="B119" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="E119" s="0" t="s">
+      <c r="E119" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="F119" s="0" t="s">
+      <c r="F119" s="2" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="A120" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B120" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C120" s="0" t="s">
+      <c r="B120" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="E120" s="0" t="s">
+      <c r="E120" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="F120" s="0" t="s">
+      <c r="F120" s="2" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="A121" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="B121" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C121" s="0" t="s">
+      <c r="B121" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="E121" s="0" t="s">
+      <c r="E121" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="F121" s="0" t="s">
+      <c r="F121" s="2" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="A122" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="B122" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C122" s="0" t="s">
+      <c r="B122" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="E122" s="0" t="s">
+      <c r="E122" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="F122" s="0" t="s">
+      <c r="F122" s="2" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="A123" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B123" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C123" s="0" t="s">
+      <c r="B123" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="E123" s="0" t="s">
+      <c r="E123" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="F123" s="0" t="s">
+      <c r="F123" s="2" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="A124" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="B124" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C124" s="0" t="s">
+      <c r="B124" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="E124" s="0" t="s">
+      <c r="E124" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="F124" s="0" t="s">
+      <c r="F124" s="2" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="A125" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="B125" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C125" s="0" t="s">
+      <c r="B125" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="E125" s="0" t="s">
+      <c r="E125" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="F125" s="0" t="s">
+      <c r="F125" s="2" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="A126" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B126" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C126" s="0" t="s">
+      <c r="B126" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="E126" s="0" t="s">
+      <c r="E126" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="F126" s="0" t="s">
+      <c r="F126" s="2" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="A127" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="B127" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C127" s="0" t="s">
+      <c r="B127" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="E127" s="0" t="s">
+      <c r="E127" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F127" s="0" t="s">
+      <c r="F127" s="2" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="A128" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="B128" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C128" s="0" t="s">
+      <c r="B128" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E128" s="0" t="s">
+      <c r="E128" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="F128" s="0" t="s">
+      <c r="F128" s="2" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="A129" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="B129" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C129" s="0" t="s">
+      <c r="B129" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="E129" s="0" t="s">
+      <c r="E129" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="F129" s="0" t="s">
+      <c r="F129" s="2" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="A130" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="B130" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C130" s="0" t="s">
+      <c r="B130" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="E130" s="0" t="s">
+      <c r="E130" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="F130" s="0" t="s">
+      <c r="F130" s="2" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="A131" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B131" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C131" s="0" t="s">
+      <c r="B131" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="E131" s="0" t="s">
+      <c r="E131" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="F131" s="0" t="s">
+      <c r="F131" s="2" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="A132" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="B132" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C132" s="0" t="s">
+      <c r="B132" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="E132" s="0" t="s">
+      <c r="E132" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="F132" s="0" t="s">
+      <c r="F132" s="2" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+      <c r="A133" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="B133" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C133" s="0" t="s">
+      <c r="B133" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="E133" s="0" t="s">
+      <c r="E133" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="F133" s="0" t="s">
+      <c r="F133" s="2" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+      <c r="A134" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B134" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="C134" s="0" t="s">
+      <c r="B134" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E134" s="0" t="s">
+      <c r="E134" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="F134" s="0" t="s">
+      <c r="F134" s="2" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+      <c r="A135" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C135" s="0" t="s">
+      <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E135" s="0" t="s">
+      <c r="E135" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F135" s="0" t="s">
+      <c r="F135" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+      <c r="A136" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C136" s="0" t="s">
+      <c r="C136" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E136" s="0" t="s">
+      <c r="E136" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F136" s="0" t="s">
+      <c r="F136" s="2" t="s">
         <v>31</v>
       </c>
     </row>
